--- a/data/nzd0555/nzd0555.xlsx
+++ b/data/nzd0555/nzd0555.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J223"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8356,6 +8356,38 @@
         <v>284.77</v>
       </c>
       <c r="J223" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>218.48</v>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="n">
+        <v>265.53</v>
+      </c>
+      <c r="F224" t="n">
+        <v>262.02</v>
+      </c>
+      <c r="G224" t="n">
+        <v>271.41</v>
+      </c>
+      <c r="H224" t="n">
+        <v>275.72</v>
+      </c>
+      <c r="I224" t="n">
+        <v>284.48</v>
+      </c>
+      <c r="J224" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8372,7 +8404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B318"/>
+  <dimension ref="A1:B319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11555,6 +11587,16 @@
       </c>
       <c r="B318" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -11723,28 +11765,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7013357521817238</v>
+        <v>-0.7593891686642468</v>
       </c>
       <c r="J2" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K2" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08288092791081492</v>
+        <v>0.09203897590953969</v>
       </c>
       <c r="M2" t="n">
-        <v>14.07734314437616</v>
+        <v>14.37217838607361</v>
       </c>
       <c r="N2" t="n">
-        <v>328.1985838634648</v>
+        <v>345.2064608882165</v>
       </c>
       <c r="O2" t="n">
-        <v>18.11625192647378</v>
+        <v>18.57973253005049</v>
       </c>
       <c r="P2" t="n">
-        <v>301.0982720061361</v>
+        <v>301.6841374461029</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11808,7 +11850,7 @@
         <v>0.3155283298477687</v>
       </c>
       <c r="J3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -11890,7 +11932,7 @@
         <v>-0.3507613891211495</v>
       </c>
       <c r="J4" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K4" t="n">
         <v>216</v>
@@ -11965,28 +12007,28 @@
         <v>0.039</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3133115131170004</v>
+        <v>-0.3229426629666902</v>
       </c>
       <c r="J5" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02160539457782706</v>
+        <v>0.02313594412190212</v>
       </c>
       <c r="M5" t="n">
-        <v>12.79393189690566</v>
+        <v>12.78909782684815</v>
       </c>
       <c r="N5" t="n">
-        <v>261.3223244050484</v>
+        <v>260.5780467308555</v>
       </c>
       <c r="O5" t="n">
-        <v>16.1654670333105</v>
+        <v>16.14243001319366</v>
       </c>
       <c r="P5" t="n">
-        <v>284.2389042181032</v>
+        <v>284.3374681614781</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12043,28 +12085,28 @@
         <v>0.0732</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2888250913992032</v>
+        <v>-0.3036263635372243</v>
       </c>
       <c r="J6" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K6" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02690097122627255</v>
+        <v>0.02977375747049404</v>
       </c>
       <c r="M6" t="n">
-        <v>10.70184181830904</v>
+        <v>10.74026821316842</v>
       </c>
       <c r="N6" t="n">
-        <v>180.6850312376098</v>
+        <v>181.0364887975282</v>
       </c>
       <c r="O6" t="n">
-        <v>13.44191322831723</v>
+        <v>13.45498007421521</v>
       </c>
       <c r="P6" t="n">
-        <v>285.9902762312908</v>
+        <v>286.1399237845354</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12121,28 +12163,28 @@
         <v>0.0585</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4493862329119679</v>
+        <v>-0.4529824504887446</v>
       </c>
       <c r="J7" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07092762628310667</v>
+        <v>0.07266862227325255</v>
       </c>
       <c r="M7" t="n">
-        <v>9.876686649658843</v>
+        <v>9.849093393440222</v>
       </c>
       <c r="N7" t="n">
-        <v>159.5529475657994</v>
+        <v>158.8977240557086</v>
       </c>
       <c r="O7" t="n">
-        <v>12.63142698058297</v>
+        <v>12.60546405554784</v>
       </c>
       <c r="P7" t="n">
-        <v>287.6235529413171</v>
+        <v>287.6599861634238</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12199,28 +12241,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2331584834130898</v>
+        <v>-0.2369398966887725</v>
       </c>
       <c r="J8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K8" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02270390453986837</v>
+        <v>0.02366039720922575</v>
       </c>
       <c r="M8" t="n">
-        <v>8.717813532584819</v>
+        <v>8.698401006871395</v>
       </c>
       <c r="N8" t="n">
-        <v>141.1429658440408</v>
+        <v>140.5795531184711</v>
       </c>
       <c r="O8" t="n">
-        <v>11.88036050985157</v>
+        <v>11.85662486201158</v>
       </c>
       <c r="P8" t="n">
-        <v>286.2780732859476</v>
+        <v>286.3163827226847</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12277,28 +12319,28 @@
         <v>0.0341</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5110456581067044</v>
+        <v>-0.5163542182933253</v>
       </c>
       <c r="J9" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K9" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04656427049319867</v>
+        <v>0.04795212829357054</v>
       </c>
       <c r="M9" t="n">
-        <v>14.17791522580253</v>
+        <v>14.14276136302122</v>
       </c>
       <c r="N9" t="n">
-        <v>327.4205153432325</v>
+        <v>326.0874980915517</v>
       </c>
       <c r="O9" t="n">
-        <v>18.0947648601255</v>
+        <v>18.05789295824825</v>
       </c>
       <c r="P9" t="n">
-        <v>304.3290247709239</v>
+        <v>304.3821108501774</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12336,7 +12378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J223"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23707,6 +23749,50 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>-46.62215983877987,169.28659474615174</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-46.62246639256892,169.2838471413381</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-46.622396788378296,169.28295486715447</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-46.622442644276084,169.2820467302689</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-46.622443032012946,169.2811448389877</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-46.62248324876783,169.28023747365546</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0555/nzd0555.xlsx
+++ b/data/nzd0555/nzd0555.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J224"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>218.48</v>
+        <v>232.76</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr"/>
@@ -8390,6 +8390,42 @@
       <c r="J224" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>242.95</v>
+      </c>
+      <c r="C225" t="n">
+        <v>248.27</v>
+      </c>
+      <c r="D225" t="n">
+        <v>253.15</v>
+      </c>
+      <c r="E225" t="n">
+        <v>256.64</v>
+      </c>
+      <c r="F225" t="n">
+        <v>261.02</v>
+      </c>
+      <c r="G225" t="n">
+        <v>268.48</v>
+      </c>
+      <c r="H225" t="n">
+        <v>267.07</v>
+      </c>
+      <c r="I225" t="n">
+        <v>284.48</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11597,6 +11633,16 @@
       </c>
       <c r="B319" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>-0.98</v>
       </c>
     </row>
   </sheetData>
@@ -11765,28 +11811,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7593891686642468</v>
+        <v>-0.7809825451271888</v>
       </c>
       <c r="J2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09203897590953969</v>
+        <v>0.09795777318176291</v>
       </c>
       <c r="M2" t="n">
-        <v>14.37217838607361</v>
+        <v>14.44169517681834</v>
       </c>
       <c r="N2" t="n">
-        <v>345.2064608882165</v>
+        <v>342.9509791616388</v>
       </c>
       <c r="O2" t="n">
-        <v>18.57973253005049</v>
+        <v>18.5189356919246</v>
       </c>
       <c r="P2" t="n">
-        <v>301.6841374461029</v>
+        <v>301.9030232034649</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11847,28 +11893,28 @@
         <v>0.0285</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3155283298477687</v>
+        <v>0.2751609276254512</v>
       </c>
       <c r="J3" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0271180365919218</v>
+        <v>0.02021090576478979</v>
       </c>
       <c r="M3" t="n">
-        <v>11.86506959363294</v>
+        <v>12.08179064450022</v>
       </c>
       <c r="N3" t="n">
-        <v>218.7008506316903</v>
+        <v>226.2767350002468</v>
       </c>
       <c r="O3" t="n">
-        <v>14.78853781249824</v>
+        <v>15.04249763171817</v>
       </c>
       <c r="P3" t="n">
-        <v>282.5001919860351</v>
+        <v>282.9012130140985</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -11929,28 +11975,28 @@
         <v>0.0308</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3507613891211495</v>
+        <v>-0.3758507183775987</v>
       </c>
       <c r="J4" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K4" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04143586734521876</v>
+        <v>0.0469256651319826</v>
       </c>
       <c r="M4" t="n">
-        <v>10.55794043161359</v>
+        <v>10.64506095465584</v>
       </c>
       <c r="N4" t="n">
-        <v>165.321931771472</v>
+        <v>167.7799596736652</v>
       </c>
       <c r="O4" t="n">
-        <v>12.85775764942986</v>
+        <v>12.95299037572657</v>
       </c>
       <c r="P4" t="n">
-        <v>289.3218270602091</v>
+        <v>289.5806657831502</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12007,28 +12053,28 @@
         <v>0.039</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3229426629666902</v>
+        <v>-0.3405944981089822</v>
       </c>
       <c r="J5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02313594412190212</v>
+        <v>0.02578963096276776</v>
       </c>
       <c r="M5" t="n">
-        <v>12.78909782684815</v>
+        <v>12.82956537804553</v>
       </c>
       <c r="N5" t="n">
-        <v>260.5780467308555</v>
+        <v>261.0079036600484</v>
       </c>
       <c r="O5" t="n">
-        <v>16.14243001319366</v>
+        <v>16.15573903168928</v>
       </c>
       <c r="P5" t="n">
-        <v>284.3374681614781</v>
+        <v>284.5185985675986</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12085,28 +12131,28 @@
         <v>0.0732</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3036263635372243</v>
+        <v>-0.3189360164183701</v>
       </c>
       <c r="J6" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02977375747049404</v>
+        <v>0.0328721310703205</v>
       </c>
       <c r="M6" t="n">
-        <v>10.74026821316842</v>
+        <v>10.78093058821621</v>
       </c>
       <c r="N6" t="n">
-        <v>181.0364887975282</v>
+        <v>181.4932492644991</v>
       </c>
       <c r="O6" t="n">
-        <v>13.45498007421521</v>
+        <v>13.47194303968433</v>
       </c>
       <c r="P6" t="n">
-        <v>286.1399237845354</v>
+        <v>286.2951346666122</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12163,28 +12209,28 @@
         <v>0.0585</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4529824504887446</v>
+        <v>-0.4590459856865658</v>
       </c>
       <c r="J7" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K7" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07266862227325255</v>
+        <v>0.07511910742687999</v>
       </c>
       <c r="M7" t="n">
-        <v>9.849093393440222</v>
+        <v>9.833557073277118</v>
       </c>
       <c r="N7" t="n">
-        <v>158.8977240557086</v>
+        <v>158.3870149823806</v>
       </c>
       <c r="O7" t="n">
-        <v>12.60546405554784</v>
+        <v>12.58519030378089</v>
       </c>
       <c r="P7" t="n">
-        <v>287.6599861634238</v>
+        <v>287.7215873829623</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12241,28 +12287,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2369398966887725</v>
+        <v>-0.24823788327654</v>
       </c>
       <c r="J8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K8" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02366039720922575</v>
+        <v>0.02604531923117792</v>
       </c>
       <c r="M8" t="n">
-        <v>8.698401006871395</v>
+        <v>8.722517886011797</v>
       </c>
       <c r="N8" t="n">
-        <v>140.5795531184711</v>
+        <v>140.6750184943514</v>
       </c>
       <c r="O8" t="n">
-        <v>11.85662486201158</v>
+        <v>11.86065000302898</v>
       </c>
       <c r="P8" t="n">
-        <v>286.3163827226847</v>
+        <v>286.4311622579608</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12319,28 +12365,28 @@
         <v>0.0341</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5163542182933253</v>
+        <v>-0.5215027296777723</v>
       </c>
       <c r="J9" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K9" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04795212829357054</v>
+        <v>0.04933710197267849</v>
       </c>
       <c r="M9" t="n">
-        <v>14.14276136302122</v>
+        <v>14.10745425783827</v>
       </c>
       <c r="N9" t="n">
-        <v>326.0874980915517</v>
+        <v>324.7599856763703</v>
       </c>
       <c r="O9" t="n">
-        <v>18.05789295824825</v>
+        <v>18.02109834822424</v>
       </c>
       <c r="P9" t="n">
-        <v>304.3821108501774</v>
+        <v>304.4337420418875</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12378,7 +12424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J224"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23757,7 +23803,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>-46.62215983877987,169.28659474615174</t>
+          <t>-46.62228765115317,169.28657719313964</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -23790,6 +23836,58 @@
       <c r="J224" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>-46.622378856196555,169.28656466750408</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>-46.6223882845538,169.28566153966418</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>-46.622393774581376,169.28475895169217</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-46.62238682340179,169.28385807176426</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-46.62238783797665,169.2829560967737</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-46.622416419631946,169.28205033335752</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-46.622365611229526,169.2811554769611</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-46.62248324876783,169.28023747365546</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
